--- a/ΠΡΟΟΔΟΣ_ΣΥΛΛΟΓΗΣ_2026.xlsx
+++ b/ΠΡΟΟΔΟΣ_ΣΥΛΛΟΓΗΣ_2026.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Ημερήσια Πρόοδος" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Σύνοψη ανά μήνα" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +31,15 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,7 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C0392B"/>
+        <fgColor rgb="001F4E5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAEFF2"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,28 +67,35 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00B7C3C9"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00B7C3C9"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00B7C3C9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00B7C3C9"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -152,6 +172,287 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Νέα links ανά ημέρα — Δασικές Πυρκαγιές Ελλάδα 2026</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Ημερήσια Πρόοδος'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Ημερήσια Πρόοδος'!$A$3:$A$108</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Ημερήσια Πρόοδος'!$B$2:$B$108</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="40"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Ημερομηνία</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="3"/>
+        <tickMarkSkip val="3"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Αριθμός links</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Σωρευτικό σύνολο συνδέσμων</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Ημερήσια Πρόοδος'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Ημερήσια Πρόοδος'!$A$3:$A$108</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Ημερήσια Πρόοδος'!$C$2:$C$108</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Ημερομηνία</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="3"/>
+        <tickMarkSkip val="3"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Σύνολο links</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="12240000" cy="3420000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="12240000" cy="3420000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -443,12 +744,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,14 +772,1575 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>— (μόνιμες)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>01/05</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>02/05</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>03/05</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>04/05</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>05/05</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>06/05</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>07/05</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>08/05</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>09/05</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>10/05</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>11/05</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>12/05</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>13/05</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>14/05</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>15/05</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>16/05</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>17/05</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>18/05</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>19/05</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>20/05</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>21/05</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>22/05</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>23/05</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>24/05</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>25/05</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>26/05</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>27/05</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>28/05</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>29/05</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>30/05</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>31/05</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>01/06</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>02/06</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>03/06</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>04/06</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>05/06</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>06/06</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>07/06</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>08/06</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>09/06</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>10/06</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>11/06</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>12/06</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>13/06</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>14/06</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>15/06</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>16/06</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>17/06</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>18/06</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>19/06</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>20/06</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>21/06</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>22/06</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>23/06</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>24/06</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>25/06</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>26/06</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>27/06</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>28/06</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>29/06</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>30/06</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>01/07</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>02/07</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>03/07</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>04/07</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>05/07</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>06/07</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>07/07</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>08/07</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>09/07</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>10/07</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>11/07</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>12/07</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>13/07</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>14/07</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>15/07</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>16/07</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>17/07</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>18/07</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>19/07</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>20/07</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>21/07</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>22/07</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>23/07</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>24/07</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>25/07</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>26/07</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>27/07</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>28/07</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>29/07</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>30/07</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>01/08</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>02/08</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>03/08</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>04/08</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>05/08</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>06/08</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>07/08</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>08/08</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>09/08</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>10/08</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>11/08</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>12/08</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>13/08</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
           <t>14/08</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B108" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C108" s="3" t="n">
         <v>334</v>
       </c>
-      <c r="C2" s="2" t="n">
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Μήνας</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Links</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Ημέρες με links</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Μέγιστο ημέρας</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ημερομηνία μεγίστου</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Μάιος 2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>01/05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Ιούνιος 2026</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>27/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Ιούλιος 2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Αύγουστος 2026</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>01/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Μόνιμες / ζωντανές πηγές</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>ΣΥΝΟΛΟ</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
         <v>334</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/ΠΡΟΟΔΟΣ_ΣΥΛΛΟΓΗΣ_2026.xlsx
+++ b/ΠΡΟΟΔΟΣ_ΣΥΛΛΟΓΗΣ_2026.xlsx
@@ -186,7 +186,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Νέα links ανά ημέρα — Δασικές Πυρκαγιές Ελλάδα 2026</a:t>
+              <a:t>Νέα links ανά ημέρα ανά πηγή — Δασικές Πυρκαγιές Ελλάδα 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -195,13 +195,13 @@
     <plotArea>
       <barChart>
         <barDir val="col"/>
-        <grouping val="clustered"/>
+        <grouping val="stacked"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Ημερήσια Πρόοδος'!B1</f>
+              <f>'Ημερήσια Πρόοδος'!C1</f>
             </strRef>
           </tx>
           <spPr>
@@ -216,11 +216,36 @@
           </cat>
           <val>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$B$2:$B$108</f>
+              <f>'Ημερήσια Πρόοδος'!$C$2:$C$108</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Ημερήσια Πρόοδος'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Ημερήσια Πρόοδος'!$A$3:$A$108</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Ημερήσια Πρόοδος'!$D$2:$D$108</f>
             </numRef>
           </val>
         </ser>
         <gapWidth val="40"/>
+        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -281,6 +306,9 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -313,7 +341,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Ημερήσια Πρόοδος'!C1</f>
+              <f>'Ημερήσια Πρόοδος'!E1</f>
             </strRef>
           </tx>
           <spPr>
@@ -336,7 +364,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$C$2:$C$108</f>
+              <f>'Ημερήσια Πρόοδος'!$E$2:$E$108</f>
             </numRef>
           </val>
         </ser>
@@ -410,7 +438,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -432,7 +460,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>21</row>
       <rowOff>0</rowOff>
@@ -744,12 +772,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -765,6 +795,16 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Λοιπές πηγές (web)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>via Yutori Scout</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Σύνολο Links</t>
         </is>
       </c>
@@ -781,6 +821,12 @@
       <c r="C2" s="2" t="n">
         <v>11</v>
       </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -792,6 +838,12 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>21</v>
       </c>
     </row>
@@ -805,6 +857,12 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -818,6 +876,12 @@
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -831,6 +895,12 @@
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -844,6 +914,12 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -857,6 +933,12 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -870,6 +952,12 @@
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -883,6 +971,12 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -896,6 +990,12 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -909,6 +1009,12 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -922,6 +1028,12 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -935,6 +1047,12 @@
         <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -948,6 +1066,12 @@
         <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -961,6 +1085,12 @@
         <v>0</v>
       </c>
       <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -974,6 +1104,12 @@
         <v>0</v>
       </c>
       <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -987,6 +1123,12 @@
         <v>0</v>
       </c>
       <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1000,6 +1142,12 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1013,6 +1161,12 @@
         <v>1</v>
       </c>
       <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1026,6 +1180,12 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1039,6 +1199,12 @@
         <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1052,6 +1218,12 @@
         <v>7</v>
       </c>
       <c r="C23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1065,6 +1237,12 @@
         <v>0</v>
       </c>
       <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1078,6 +1256,12 @@
         <v>0</v>
       </c>
       <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1091,6 +1275,12 @@
         <v>2</v>
       </c>
       <c r="C26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="n">
         <v>32</v>
       </c>
     </row>
@@ -1104,6 +1294,12 @@
         <v>0</v>
       </c>
       <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>32</v>
       </c>
     </row>
@@ -1117,6 +1313,12 @@
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
         <v>33</v>
       </c>
     </row>
@@ -1130,6 +1332,12 @@
         <v>0</v>
       </c>
       <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="n">
         <v>33</v>
       </c>
     </row>
@@ -1143,6 +1351,12 @@
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="n">
         <v>34</v>
       </c>
     </row>
@@ -1156,6 +1370,12 @@
         <v>2</v>
       </c>
       <c r="C31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
         <v>36</v>
       </c>
     </row>
@@ -1169,6 +1389,12 @@
         <v>3</v>
       </c>
       <c r="C32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>39</v>
       </c>
     </row>
@@ -1182,6 +1408,12 @@
         <v>6</v>
       </c>
       <c r="C33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="n">
         <v>45</v>
       </c>
     </row>
@@ -1195,6 +1427,12 @@
         <v>4</v>
       </c>
       <c r="C34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="3" t="n">
         <v>49</v>
       </c>
     </row>
@@ -1208,6 +1446,12 @@
         <v>1</v>
       </c>
       <c r="C35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1221,6 +1465,12 @@
         <v>5</v>
       </c>
       <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1234,6 +1484,12 @@
         <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1247,6 +1503,12 @@
         <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1260,6 +1522,12 @@
         <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1273,6 +1541,12 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1286,6 +1560,12 @@
         <v>5</v>
       </c>
       <c r="C41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1299,6 +1579,12 @@
         <v>3</v>
       </c>
       <c r="C42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" s="3" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1312,6 +1598,12 @@
         <v>3</v>
       </c>
       <c r="C43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="3" t="n">
         <v>66</v>
       </c>
     </row>
@@ -1325,6 +1617,12 @@
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="3" t="n">
         <v>67</v>
       </c>
     </row>
@@ -1338,6 +1636,12 @@
         <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
         <v>67</v>
       </c>
     </row>
@@ -1351,6 +1655,12 @@
         <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
         <v>67</v>
       </c>
     </row>
@@ -1364,6 +1674,12 @@
         <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
         <v>67</v>
       </c>
     </row>
@@ -1377,6 +1693,12 @@
         <v>2</v>
       </c>
       <c r="C48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="n">
         <v>69</v>
       </c>
     </row>
@@ -1390,6 +1712,12 @@
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1403,6 +1731,12 @@
         <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1416,6 +1750,12 @@
         <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1429,6 +1769,12 @@
         <v>0</v>
       </c>
       <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1442,6 +1788,12 @@
         <v>9</v>
       </c>
       <c r="C53" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
         <v>79</v>
       </c>
     </row>
@@ -1455,6 +1807,12 @@
         <v>8</v>
       </c>
       <c r="C54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
         <v>87</v>
       </c>
     </row>
@@ -1468,6 +1826,12 @@
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="3" t="n">
         <v>88</v>
       </c>
     </row>
@@ -1481,6 +1845,12 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
         <v>88</v>
       </c>
     </row>
@@ -1494,6 +1864,12 @@
         <v>1</v>
       </c>
       <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="3" t="n">
         <v>89</v>
       </c>
     </row>
@@ -1507,6 +1883,12 @@
         <v>0</v>
       </c>
       <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
         <v>89</v>
       </c>
     </row>
@@ -1520,6 +1902,12 @@
         <v>1</v>
       </c>
       <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="3" t="n">
         <v>90</v>
       </c>
     </row>
@@ -1533,6 +1921,12 @@
         <v>9</v>
       </c>
       <c r="C60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E60" s="3" t="n">
         <v>99</v>
       </c>
     </row>
@@ -1546,6 +1940,12 @@
         <v>7</v>
       </c>
       <c r="C61" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="3" t="n">
         <v>106</v>
       </c>
     </row>
@@ -1559,6 +1959,12 @@
         <v>2</v>
       </c>
       <c r="C62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="3" t="n">
         <v>108</v>
       </c>
     </row>
@@ -1572,6 +1978,12 @@
         <v>0</v>
       </c>
       <c r="C63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="3" t="n">
         <v>108</v>
       </c>
     </row>
@@ -1585,6 +1997,12 @@
         <v>7</v>
       </c>
       <c r="C64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E64" s="3" t="n">
         <v>115</v>
       </c>
     </row>
@@ -1598,6 +2016,12 @@
         <v>0</v>
       </c>
       <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
         <v>115</v>
       </c>
     </row>
@@ -1611,6 +2035,12 @@
         <v>2</v>
       </c>
       <c r="C66" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
         <v>117</v>
       </c>
     </row>
@@ -1624,6 +2054,12 @@
         <v>3</v>
       </c>
       <c r="C67" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1637,6 +2073,12 @@
         <v>4</v>
       </c>
       <c r="C68" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" s="3" t="n">
         <v>124</v>
       </c>
     </row>
@@ -1650,6 +2092,12 @@
         <v>10</v>
       </c>
       <c r="C69" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E69" s="3" t="n">
         <v>134</v>
       </c>
     </row>
@@ -1663,6 +2111,12 @@
         <v>1</v>
       </c>
       <c r="C70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
         <v>135</v>
       </c>
     </row>
@@ -1676,6 +2130,12 @@
         <v>3</v>
       </c>
       <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E71" s="3" t="n">
         <v>138</v>
       </c>
     </row>
@@ -1689,6 +2149,12 @@
         <v>0</v>
       </c>
       <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
         <v>138</v>
       </c>
     </row>
@@ -1702,6 +2168,12 @@
         <v>1</v>
       </c>
       <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="3" t="n">
         <v>139</v>
       </c>
     </row>
@@ -1715,6 +2187,12 @@
         <v>3</v>
       </c>
       <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" s="3" t="n">
         <v>142</v>
       </c>
     </row>
@@ -1728,6 +2206,12 @@
         <v>1</v>
       </c>
       <c r="C75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
         <v>143</v>
       </c>
     </row>
@@ -1741,6 +2225,12 @@
         <v>0</v>
       </c>
       <c r="C76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="3" t="n">
         <v>143</v>
       </c>
     </row>
@@ -1754,6 +2244,12 @@
         <v>0</v>
       </c>
       <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
         <v>143</v>
       </c>
     </row>
@@ -1767,6 +2263,12 @@
         <v>0</v>
       </c>
       <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
         <v>143</v>
       </c>
     </row>
@@ -1780,6 +2282,12 @@
         <v>2</v>
       </c>
       <c r="C79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="3" t="n">
         <v>145</v>
       </c>
     </row>
@@ -1793,6 +2301,12 @@
         <v>0</v>
       </c>
       <c r="C80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="3" t="n">
         <v>145</v>
       </c>
     </row>
@@ -1806,6 +2320,12 @@
         <v>2</v>
       </c>
       <c r="C81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
         <v>147</v>
       </c>
     </row>
@@ -1819,6 +2339,12 @@
         <v>3</v>
       </c>
       <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" s="3" t="n">
         <v>150</v>
       </c>
     </row>
@@ -1832,6 +2358,12 @@
         <v>1</v>
       </c>
       <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="3" t="n">
         <v>151</v>
       </c>
     </row>
@@ -1845,6 +2377,12 @@
         <v>1</v>
       </c>
       <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="3" t="n">
         <v>152</v>
       </c>
     </row>
@@ -1858,6 +2396,12 @@
         <v>1</v>
       </c>
       <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="3" t="n">
         <v>153</v>
       </c>
     </row>
@@ -1871,6 +2415,12 @@
         <v>5</v>
       </c>
       <c r="C86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E86" s="3" t="n">
         <v>158</v>
       </c>
     </row>
@@ -1884,6 +2434,12 @@
         <v>3</v>
       </c>
       <c r="C87" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="3" t="n">
         <v>161</v>
       </c>
     </row>
@@ -1897,6 +2453,12 @@
         <v>3</v>
       </c>
       <c r="C88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" s="3" t="n">
         <v>164</v>
       </c>
     </row>
@@ -1910,6 +2472,12 @@
         <v>2</v>
       </c>
       <c r="C89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="3" t="n">
         <v>166</v>
       </c>
     </row>
@@ -1923,6 +2491,12 @@
         <v>0</v>
       </c>
       <c r="C90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="3" t="n">
         <v>166</v>
       </c>
     </row>
@@ -1936,6 +2510,12 @@
         <v>2</v>
       </c>
       <c r="C91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="3" t="n">
         <v>168</v>
       </c>
     </row>
@@ -1949,6 +2529,12 @@
         <v>13</v>
       </c>
       <c r="C92" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E92" s="3" t="n">
         <v>181</v>
       </c>
     </row>
@@ -1962,6 +2548,12 @@
         <v>15</v>
       </c>
       <c r="C93" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E93" s="3" t="n">
         <v>196</v>
       </c>
     </row>
@@ -1975,6 +2567,12 @@
         <v>15</v>
       </c>
       <c r="C94" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" s="3" t="n">
         <v>211</v>
       </c>
     </row>
@@ -1988,6 +2586,12 @@
         <v>20</v>
       </c>
       <c r="C95" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="3" t="n">
         <v>231</v>
       </c>
     </row>
@@ -2001,6 +2605,12 @@
         <v>12</v>
       </c>
       <c r="C96" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" s="3" t="n">
         <v>243</v>
       </c>
     </row>
@@ -2014,6 +2624,12 @@
         <v>11</v>
       </c>
       <c r="C97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" s="3" t="n">
         <v>254</v>
       </c>
     </row>
@@ -2027,6 +2643,12 @@
         <v>11</v>
       </c>
       <c r="C98" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" s="3" t="n">
         <v>265</v>
       </c>
     </row>
@@ -2040,6 +2662,12 @@
         <v>3</v>
       </c>
       <c r="C99" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="3" t="n">
         <v>268</v>
       </c>
     </row>
@@ -2053,6 +2681,12 @@
         <v>3</v>
       </c>
       <c r="C100" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="3" t="n">
         <v>271</v>
       </c>
     </row>
@@ -2066,6 +2700,12 @@
         <v>4</v>
       </c>
       <c r="C101" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="n">
         <v>275</v>
       </c>
     </row>
@@ -2079,6 +2719,12 @@
         <v>8</v>
       </c>
       <c r="C102" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E102" s="3" t="n">
         <v>283</v>
       </c>
     </row>
@@ -2092,6 +2738,12 @@
         <v>4</v>
       </c>
       <c r="C103" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="3" t="n">
         <v>287</v>
       </c>
     </row>
@@ -2105,6 +2757,12 @@
         <v>8</v>
       </c>
       <c r="C104" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="3" t="n">
         <v>295</v>
       </c>
     </row>
@@ -2118,6 +2776,12 @@
         <v>6</v>
       </c>
       <c r="C105" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
         <v>301</v>
       </c>
     </row>
@@ -2131,6 +2795,12 @@
         <v>6</v>
       </c>
       <c r="C106" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="3" t="n">
         <v>307</v>
       </c>
     </row>
@@ -2144,6 +2814,12 @@
         <v>19</v>
       </c>
       <c r="C107" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" s="3" t="n">
         <v>326</v>
       </c>
     </row>
@@ -2157,6 +2833,12 @@
         <v>8</v>
       </c>
       <c r="C108" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="3" t="n">
         <v>334</v>
       </c>
     </row>
@@ -2172,14 +2854,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2195,15 +2878,20 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
+          <t>εκ των οποίων via Yutori</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
           <t>Ημέρες με links</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Μέγιστο ημέρας</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Ημερομηνία μεγίστου</t>
         </is>
@@ -2219,12 +2907,15 @@
         <v>34</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>01/05</t>
         </is>
@@ -2240,12 +2931,15 @@
         <v>63</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>27/06</t>
         </is>
@@ -2261,12 +2955,15 @@
         <v>103</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>31/07</t>
         </is>
@@ -2282,12 +2979,15 @@
         <v>123</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>01/08</t>
         </is>
@@ -2302,17 +3002,20 @@
       <c r="B6" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2327,17 +3030,20 @@
       <c r="B7" s="5" t="n">
         <v>334</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/ΠΡΟΟΔΟΣ_ΣΥΛΛΟΓΗΣ_2026.xlsx
+++ b/ΠΡΟΟΔΟΣ_ΣΥΛΛΟΓΗΣ_2026.xlsx
@@ -186,7 +186,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Νέα links ανά ημέρα ανά πηγή — Δασικές Πυρκαγιές Ελλάδα 2026</a:t>
+              <a:t>Νέα links ανά ημέρα — Δασικές Πυρκαγιές Ελλάδα 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -195,13 +195,13 @@
     <plotArea>
       <barChart>
         <barDir val="col"/>
-        <grouping val="stacked"/>
+        <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Ημερήσια Πρόοδος'!C1</f>
+              <f>'Ημερήσια Πρόοδος'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -216,36 +216,11 @@
           </cat>
           <val>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$C$2:$C$108</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Ημερήσια Πρόοδος'!D1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Ημερήσια Πρόοδος'!$A$3:$A$108</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Ημερήσια Πρόοδος'!$D$2:$D$108</f>
+              <f>'Ημερήσια Πρόοδος'!$B$2:$B$108</f>
             </numRef>
           </val>
         </ser>
         <gapWidth val="40"/>
-        <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -306,9 +281,6 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -341,7 +313,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Ημερήσια Πρόοδος'!E1</f>
+              <f>'Ημερήσια Πρόοδος'!C1</f>
             </strRef>
           </tx>
           <spPr>
@@ -364,7 +336,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$E$2:$E$108</f>
+              <f>'Ημερήσια Πρόοδος'!$C$2:$C$108</f>
             </numRef>
           </val>
         </ser>
@@ -438,7 +410,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -460,7 +432,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>21</row>
       <rowOff>0</rowOff>
@@ -772,14 +744,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -795,16 +765,6 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Λοιπές πηγές (web)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>via Yutori Scout</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>Σύνολο Links</t>
         </is>
       </c>
@@ -821,12 +781,6 @@
       <c r="C2" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>11</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -838,12 +792,6 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n">
         <v>21</v>
       </c>
     </row>
@@ -857,12 +805,6 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -876,12 +818,6 @@
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -895,12 +831,6 @@
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -914,12 +844,6 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -933,12 +857,6 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -952,12 +870,6 @@
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -971,12 +883,6 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -990,12 +896,6 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1009,12 +909,6 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1028,12 +922,6 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1047,12 +935,6 @@
         <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1066,12 +948,6 @@
         <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1085,12 +961,6 @@
         <v>0</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1104,12 +974,6 @@
         <v>0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1123,12 +987,6 @@
         <v>0</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1142,12 +1000,6 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1161,12 +1013,6 @@
         <v>1</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1180,12 +1026,6 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1199,12 +1039,6 @@
         <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1218,12 +1052,6 @@
         <v>7</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1237,12 +1065,6 @@
         <v>0</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1256,12 +1078,6 @@
         <v>0</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="3" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1275,12 +1091,6 @@
         <v>2</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3" t="n">
         <v>32</v>
       </c>
     </row>
@@ -1294,12 +1104,6 @@
         <v>0</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="3" t="n">
         <v>32</v>
       </c>
     </row>
@@ -1313,12 +1117,6 @@
         <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3" t="n">
         <v>33</v>
       </c>
     </row>
@@ -1332,12 +1130,6 @@
         <v>0</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3" t="n">
         <v>33</v>
       </c>
     </row>
@@ -1351,12 +1143,6 @@
         <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3" t="n">
         <v>34</v>
       </c>
     </row>
@@ -1370,12 +1156,6 @@
         <v>2</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="3" t="n">
         <v>36</v>
       </c>
     </row>
@@ -1389,12 +1169,6 @@
         <v>3</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3" t="n">
         <v>39</v>
       </c>
     </row>
@@ -1408,12 +1182,6 @@
         <v>6</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E33" s="3" t="n">
         <v>45</v>
       </c>
     </row>
@@ -1427,12 +1195,6 @@
         <v>4</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" s="3" t="n">
         <v>49</v>
       </c>
     </row>
@@ -1446,12 +1208,6 @@
         <v>1</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="3" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1465,12 +1221,6 @@
         <v>5</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E36" s="3" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1484,12 +1234,6 @@
         <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="3" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1503,12 +1247,6 @@
         <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="3" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1522,12 +1260,6 @@
         <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="3" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1541,12 +1273,6 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="3" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1560,12 +1286,6 @@
         <v>5</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" s="3" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1579,12 +1299,6 @@
         <v>3</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" s="3" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1598,12 +1312,6 @@
         <v>3</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" s="3" t="n">
         <v>66</v>
       </c>
     </row>
@@ -1617,12 +1325,6 @@
         <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="3" t="n">
         <v>67</v>
       </c>
     </row>
@@ -1636,12 +1338,6 @@
         <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3" t="n">
         <v>67</v>
       </c>
     </row>
@@ -1655,12 +1351,6 @@
         <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="3" t="n">
         <v>67</v>
       </c>
     </row>
@@ -1674,12 +1364,6 @@
         <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3" t="n">
         <v>67</v>
       </c>
     </row>
@@ -1693,12 +1377,6 @@
         <v>2</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3" t="n">
         <v>69</v>
       </c>
     </row>
@@ -1712,12 +1390,6 @@
         <v>1</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1731,12 +1403,6 @@
         <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="3" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1750,12 +1416,6 @@
         <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="3" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1769,12 +1429,6 @@
         <v>0</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1788,12 +1442,6 @@
         <v>9</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="3" t="n">
         <v>79</v>
       </c>
     </row>
@@ -1807,12 +1455,6 @@
         <v>8</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="3" t="n">
         <v>87</v>
       </c>
     </row>
@@ -1826,12 +1468,6 @@
         <v>1</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="3" t="n">
         <v>88</v>
       </c>
     </row>
@@ -1845,12 +1481,6 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="3" t="n">
         <v>88</v>
       </c>
     </row>
@@ -1864,12 +1494,6 @@
         <v>1</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="3" t="n">
         <v>89</v>
       </c>
     </row>
@@ -1883,12 +1507,6 @@
         <v>0</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3" t="n">
         <v>89</v>
       </c>
     </row>
@@ -1902,12 +1520,6 @@
         <v>1</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="3" t="n">
         <v>90</v>
       </c>
     </row>
@@ -1921,12 +1533,6 @@
         <v>9</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D60" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E60" s="3" t="n">
         <v>99</v>
       </c>
     </row>
@@ -1940,12 +1546,6 @@
         <v>7</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D61" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" s="3" t="n">
         <v>106</v>
       </c>
     </row>
@@ -1959,12 +1559,6 @@
         <v>2</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E62" s="3" t="n">
         <v>108</v>
       </c>
     </row>
@@ -1978,12 +1572,6 @@
         <v>0</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="3" t="n">
         <v>108</v>
       </c>
     </row>
@@ -1997,12 +1585,6 @@
         <v>7</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E64" s="3" t="n">
         <v>115</v>
       </c>
     </row>
@@ -2016,12 +1598,6 @@
         <v>0</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="3" t="n">
         <v>115</v>
       </c>
     </row>
@@ -2035,12 +1611,6 @@
         <v>2</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="3" t="n">
         <v>117</v>
       </c>
     </row>
@@ -2054,12 +1624,6 @@
         <v>3</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="3" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2073,12 +1637,6 @@
         <v>4</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E68" s="3" t="n">
         <v>124</v>
       </c>
     </row>
@@ -2092,12 +1650,6 @@
         <v>10</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D69" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E69" s="3" t="n">
         <v>134</v>
       </c>
     </row>
@@ -2111,12 +1663,6 @@
         <v>1</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="3" t="n">
         <v>135</v>
       </c>
     </row>
@@ -2130,12 +1676,6 @@
         <v>3</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E71" s="3" t="n">
         <v>138</v>
       </c>
     </row>
@@ -2149,12 +1689,6 @@
         <v>0</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="3" t="n">
         <v>138</v>
       </c>
     </row>
@@ -2168,12 +1702,6 @@
         <v>1</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="3" t="n">
         <v>139</v>
       </c>
     </row>
@@ -2187,12 +1715,6 @@
         <v>3</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E74" s="3" t="n">
         <v>142</v>
       </c>
     </row>
@@ -2206,12 +1728,6 @@
         <v>1</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="3" t="n">
         <v>143</v>
       </c>
     </row>
@@ -2225,12 +1741,6 @@
         <v>0</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="3" t="n">
         <v>143</v>
       </c>
     </row>
@@ -2244,12 +1754,6 @@
         <v>0</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="3" t="n">
         <v>143</v>
       </c>
     </row>
@@ -2263,12 +1767,6 @@
         <v>0</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="3" t="n">
         <v>143</v>
       </c>
     </row>
@@ -2282,12 +1780,6 @@
         <v>2</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="3" t="n">
         <v>145</v>
       </c>
     </row>
@@ -2301,12 +1793,6 @@
         <v>0</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" s="3" t="n">
         <v>145</v>
       </c>
     </row>
@@ -2320,12 +1806,6 @@
         <v>2</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="3" t="n">
         <v>147</v>
       </c>
     </row>
@@ -2339,12 +1819,6 @@
         <v>3</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E82" s="3" t="n">
         <v>150</v>
       </c>
     </row>
@@ -2358,12 +1832,6 @@
         <v>1</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="3" t="n">
         <v>151</v>
       </c>
     </row>
@@ -2377,12 +1845,6 @@
         <v>1</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="3" t="n">
         <v>152</v>
       </c>
     </row>
@@ -2396,12 +1858,6 @@
         <v>1</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="3" t="n">
         <v>153</v>
       </c>
     </row>
@@ -2415,12 +1871,6 @@
         <v>5</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D86" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E86" s="3" t="n">
         <v>158</v>
       </c>
     </row>
@@ -2434,12 +1884,6 @@
         <v>3</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D87" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="3" t="n">
         <v>161</v>
       </c>
     </row>
@@ -2453,12 +1897,6 @@
         <v>3</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E88" s="3" t="n">
         <v>164</v>
       </c>
     </row>
@@ -2472,12 +1910,6 @@
         <v>2</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="3" t="n">
         <v>166</v>
       </c>
     </row>
@@ -2491,12 +1923,6 @@
         <v>0</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="3" t="n">
         <v>166</v>
       </c>
     </row>
@@ -2510,12 +1936,6 @@
         <v>2</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D91" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="3" t="n">
         <v>168</v>
       </c>
     </row>
@@ -2529,12 +1949,6 @@
         <v>13</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D92" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E92" s="3" t="n">
         <v>181</v>
       </c>
     </row>
@@ -2548,12 +1962,6 @@
         <v>15</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D93" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E93" s="3" t="n">
         <v>196</v>
       </c>
     </row>
@@ -2567,12 +1975,6 @@
         <v>15</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="D94" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E94" s="3" t="n">
         <v>211</v>
       </c>
     </row>
@@ -2586,12 +1988,6 @@
         <v>20</v>
       </c>
       <c r="C95" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="D95" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" s="3" t="n">
         <v>231</v>
       </c>
     </row>
@@ -2605,12 +2001,6 @@
         <v>12</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="D96" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E96" s="3" t="n">
         <v>243</v>
       </c>
     </row>
@@ -2624,12 +2014,6 @@
         <v>11</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D97" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E97" s="3" t="n">
         <v>254</v>
       </c>
     </row>
@@ -2643,12 +2027,6 @@
         <v>11</v>
       </c>
       <c r="C98" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D98" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E98" s="3" t="n">
         <v>265</v>
       </c>
     </row>
@@ -2662,12 +2040,6 @@
         <v>3</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="3" t="n">
         <v>268</v>
       </c>
     </row>
@@ -2681,12 +2053,6 @@
         <v>3</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D100" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" s="3" t="n">
         <v>271</v>
       </c>
     </row>
@@ -2700,12 +2066,6 @@
         <v>4</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3" t="n">
         <v>275</v>
       </c>
     </row>
@@ -2719,12 +2079,6 @@
         <v>8</v>
       </c>
       <c r="C102" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D102" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E102" s="3" t="n">
         <v>283</v>
       </c>
     </row>
@@ -2738,12 +2092,6 @@
         <v>4</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D103" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" s="3" t="n">
         <v>287</v>
       </c>
     </row>
@@ -2757,12 +2105,6 @@
         <v>8</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D104" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="3" t="n">
         <v>295</v>
       </c>
     </row>
@@ -2776,12 +2118,6 @@
         <v>6</v>
       </c>
       <c r="C105" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="3" t="n">
         <v>301</v>
       </c>
     </row>
@@ -2795,12 +2131,6 @@
         <v>6</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D106" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" s="3" t="n">
         <v>307</v>
       </c>
     </row>
@@ -2814,12 +2144,6 @@
         <v>19</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="D107" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E107" s="3" t="n">
         <v>326</v>
       </c>
     </row>
@@ -2833,12 +2157,6 @@
         <v>8</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D108" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="3" t="n">
         <v>334</v>
       </c>
     </row>
@@ -2854,15 +2172,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2878,20 +2195,15 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>εκ των οποίων via Yutori</t>
+          <t>Ημέρες με links</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>Ημέρες με links</t>
+          <t>Μέγιστο ημέρας</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Μέγιστο ημέρας</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Ημερομηνία μεγίστου</t>
         </is>
@@ -2907,15 +2219,12 @@
         <v>34</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>01/05</t>
         </is>
@@ -2931,15 +2240,12 @@
         <v>63</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="E3" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>27/06</t>
         </is>
@@ -2955,15 +2261,12 @@
         <v>103</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="E4" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>31/07</t>
         </is>
@@ -2979,15 +2282,12 @@
         <v>123</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>01/08</t>
         </is>
@@ -3002,8 +2302,10 @@
       <c r="B6" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -3011,11 +2313,6 @@
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3030,8 +2327,10 @@
       <c r="B7" s="5" t="n">
         <v>334</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>101</v>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -3039,11 +2338,6 @@
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/ΠΡΟΟΔΟΣ_ΣΥΛΛΟΓΗΣ_2026.xlsx
+++ b/ΠΡΟΟΔΟΣ_ΣΥΛΛΟΓΗΣ_2026.xlsx
@@ -211,12 +211,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$A$3:$A$108</f>
+              <f>'Ημερήσια Πρόοδος'!$A$3:$A$109</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$B$2:$B$108</f>
+              <f>'Ημερήσια Πρόοδος'!$B$2:$B$109</f>
             </numRef>
           </val>
         </ser>
@@ -331,12 +331,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$A$3:$A$108</f>
+              <f>'Ημερήσια Πρόοδος'!$A$3:$A$109</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ημερήσια Πρόοδος'!$C$2:$C$108</f>
+              <f>'Ημερήσια Πρόοδος'!$C$2:$C$109</f>
             </numRef>
           </val>
         </ser>
@@ -744,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:C109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2157,19 @@
         <v>8</v>
       </c>
       <c r="C108" s="3" t="n">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>15/08</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
         <v>334</v>
       </c>
     </row>
